--- a/data/trans_orig/P25C_R2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120496</t>
+          <t>119682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>57820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64342</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180141</t>
+          <t>179467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187181</t>
+          <t>187153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89083</t>
+          <t>89630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50291</t>
+          <t>50772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55895</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141866</t>
+          <t>142628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>148612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>324372</t>
+          <t>325152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346441</t>
+          <t>346376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179406</t>
+          <t>178750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187219</t>
+          <t>187391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>73211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78395</t>
+          <t>78399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255661</t>
+          <t>256376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264475</t>
+          <t>264833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80903</t>
+          <t>80959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87107</t>
+          <t>87098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61847</t>
+          <t>61910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68293</t>
+          <t>68272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145959</t>
+          <t>146307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154477</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>43783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>816598</t>
+          <t>817049</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>834781</t>
+          <t>835689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310286</t>
+          <t>310591</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321270</t>
+          <t>321371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1132685</t>
+          <t>1131474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1158959</t>
+          <t>1157729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122755</t>
+          <t>129924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119682</t>
+          <t>127336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>66334</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63983</t>
+          <t>68706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>184803</t>
+          <t>196258</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>191728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187153</t>
+          <t>198746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92480</t>
+          <t>101670</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89630</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>59387</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>55103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55782</t>
+          <t>61520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>146514</t>
+          <t>161059</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142628</t>
+          <t>156396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148612</t>
+          <t>163749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,67 +1411,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14374</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2816</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -1524,69 +1524,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>336489</t>
+          <t>101756</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325152</t>
+          <t>97590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22017</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19541</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22682</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>86,15%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18992</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21808</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>153</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>357654</t>
+          <t>123773</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346376</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>126296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184417</t>
+          <t>205576</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178750</t>
+          <t>199598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187391</t>
+          <t>208598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73211</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78399</t>
+          <t>84386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>261118</t>
+          <t>288227</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256376</t>
+          <t>282304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264833</t>
+          <t>292178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85378</t>
+          <t>91373</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80959</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65940</t>
+          <t>75447</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>77977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>166820</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146307</t>
+          <t>161175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154568</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>37669</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>44342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38956</t>
+          <t>39298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>826980</t>
+          <t>635534</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>817049</t>
+          <t>627434</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>835689</t>
+          <t>641061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>316685</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310591</t>
+          <t>336951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321371</t>
+          <t>349231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1143665</t>
+          <t>979038</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1131474</t>
+          <t>968533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157729</t>
+          <t>986664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
